--- a/artfynd/A 41793-2020 artfynd.xlsx
+++ b/artfynd/A 41793-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41793-2020 artfynd.xlsx
+++ b/artfynd/A 41793-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,134 +1045,6 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>109057936</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57068</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100018</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Rördrom</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Botaurus stellaris</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Ålspångavassen, Ålspångaviken, Långhalsen, Srm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>593046</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6534807</v>
-      </c>
-      <c r="S5" t="n">
-        <v>125</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Flen</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Bettna</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2023-05-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2023-05-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Per Flodin</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Per Flodin</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41793-2020 artfynd.xlsx
+++ b/artfynd/A 41793-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,6 +1045,139 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124817002</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57829</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103076</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vassångare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Locustella luscinioides</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Savi, 1824)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ålspångavassen, Ålspångaviken, Långhalsen, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>593046</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6534807</v>
+      </c>
+      <c r="S5" t="n">
+        <v>125</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bettna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hördes som den satt mitt i viken.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Flodin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Flodin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41793-2020 artfynd.xlsx
+++ b/artfynd/A 41793-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1178,6 +1178,134 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125248275</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57829</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103076</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vassångare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Locustella luscinioides</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Savi, 1824)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ålspångaviken, Ålspångaviken, Långhalsen, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>593137</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6534924</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bettna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Flodin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Flodin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41793-2020 artfynd.xlsx
+++ b/artfynd/A 41793-2020 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>124817002</v>
       </c>
       <c r="B5" t="n">
-        <v>57829</v>
+        <v>57872</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>125248275</v>
       </c>
       <c r="B6" t="n">
-        <v>57829</v>
+        <v>57872</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 41793-2020 artfynd.xlsx
+++ b/artfynd/A 41793-2020 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>125248275</v>
       </c>
       <c r="B6" t="n">
-        <v>57890</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
